--- a/docs/EXECUTION_SURFACES_TOOLING.xlsx
+++ b/docs/EXECUTION_SURFACES_TOOLING.xlsx
@@ -523,8 +523,8 @@
     <row r="2" ht="195" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verdict (2026-10-16, branch claude/cloud-run-bigquery-pipeline-e94ziy at d18a95f, 42 commits since 2026-10-05): the five reusable
-skills — aider-scaffold with its diff ledger, tree-f-visualizer, pass-sequence, regen-workflow — ran on every building block of
+          <t xml:space="preserve">Verdict (2026-10-16, branch claude/cloud-run-bigquery-pipeline-e94ziy at d18a95f, 42 commits since 2026-10-05): the four reusable
+skills (five tools, counting the diff ledger inside aider-scaffold) — aider-scaffold, tree-f-visualizer, pass-sequence, regen-workflow — ran on every building block of
 CloudBQ and were installed unchanged in IC-DBT-BQ. They execute on three surfaces. D, the developer's shell on a clone, is the only
 surface that creates: it writes the recipe, applies the block (aider when an LLM key is present, by hand otherwise — in this project
 aider never answered, 17 commits carry "Scaffolded-by: hand (no LLM key)"), verifies, commits with trailers, appends the ledger,
@@ -921,7 +921,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>IC-DBT-BQ carries the four skill folders byte-identical to CloudBQ (reusability probe #2, commits a96fae0, 4f48d42, 250dc6d)</t>
+          <t>IC-DBT-BQ (250dc6d) carries the four skills' pages, scripts, references and config assets byte-identical to CloudBQ d18a95f; only aider-scaffold/assets/recipes/ differs, by design (ports be0b280, a96fae0, 041a528, 541127d)</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>at d18a95f: 12 recipes on disk; 17 commits carry a Recipe trailer; 92 annotated nodes name theirs (this page adds one recipe and three nodes)</t>
+          <t>at d18a95f: 12 recipes on disk; 17 commits carry Scaffolded-by, 13 of them also a Recipe trailer; 85 of the 92 annotated nodes name a recipe (this page adds one recipe and three nodes)</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>git log trailers: 17 Scaffolded-by, 17 Recipe; tests/test_regen_workflow.py::test_commit_step_actions_shape asserts the Regenerated-by URL</t>
+          <t>git log trailers at d18a95f: 17 Scaffolded-by, 13 Recipe (the four earliest tooling commits carry Scaffolded-by alone); tests/test_regen_workflow.py::test_commit_step_actions_shape asserts the Regenerated-by URL</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>tree_f --check: up to date on every CI run since 8d14e0d; 92 nodes; exclude: ['*.patch'] keeps the ledger out of the tree</t>
+          <t>the tree check has not failed in CI since 8d14e0d (it failed at 9d0a184 and a7e64de before; later red runs stopped earlier, at pytest: 0a54e5f, 298c7db); 92 nodes at d18a95f; exclude: ['*.patch'] keeps the ledger out of the tree</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>prospective — the same rebuild on push; not configured today</t>
+          <t>not a bot job: the builder's output is never byte-identical, so a scheduled rebuild would commit a changed file every run; the developer rebuilds when the YAML changes</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>verify: OK on execution_surfaces.yaml (Layers 2/5/6 … ), execution_surfaces_l2.yaml and this spec; the 1-byte xlsx churn observed on 2026-10-16 and reverted</t>
+          <t>verify: OK on execution_surfaces.yaml (Layers 4/4/10, steps 2/5/6), execution_surfaces_l2.yaml (Layers 0/6/9, steps 2/6/4) and this spec (Layers 1/6/5, steps 1/5/5); the 1-byte xlsx churn observed on 2026-10-16 and reverted</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>both committed workflows equal to --print output at d18a95f; actionlint 1.7.12 clean on all three workflow files</t>
+          <t>both committed workflows equal to --print output at d18a95f; actionlint 1.7.12 clean on all three workflow files on 2026-10-16 (a local run, not reproducible from the clone)</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Every confirmed finding becomes a test or a --check so C holds it afterwards (regen-workflow: 6 → 15 tests across two review rounds).</t>
+          <t>Every confirmed finding becomes a test or a --check so C holds it afterwards (regen-workflow: 13 → 15 tests between 41a9634 and 610d41e).</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>review rounds on deploy.sh (574e954), the notebooks (e88c27a) and the GitHub Actions skill (41a9634, 610d41e — three critics, 33 findings with duplicates across critics, every non-duplicate one fixed before the push and held by 15 tests)</t>
+          <t>review rounds on deploy.sh (574e954), the notebooks (e88c27a) and the GitHub Actions skill (41a9634 → 610d41e: tests 13 → 15, each new test holding one finding); the review records themselves are not kept in the repository</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>PR Wkayaobama/CloudBQ#1: every head green (c978940, 5c777c9, d18a95f); test_commit_step_retries_a_race_and_stops_on_a_refusal</t>
+          <t>PR Wkayaobama/CloudBQ#1: heads c978940, 5c777c9, d18a95f green (check on github.com; not derivable from the clone); test_commit_step_retries_a_race_and_stops_on_a_refusal</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Last local step after every block commit; re-running adds only unlisted commits.</t>
+          <t>Runs after the last commit of the block (including the docs commit of steps 6–8); re-running adds only unlisted commits.</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>prospective regen consumer</t>
+          <t>n/a — not a bot job (the output is never byte-identical)</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>8d14e0d (2026-10-14); every CI run since</t>
+          <t>8d14e0d (2026-10-14); the tree check has not failed in CI since</t>
         </is>
       </c>
     </row>
@@ -2192,17 +2192,17 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>a multi-step one-liner without a failure guard per step; no parse before write</t>
+          <t>a plain scalar containing ": " was not quoted; the spec was committed without a --verify build</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>yaml.safe_load every spec before writing; "|| fail" after each step of a chained command; the generators parse their own output before writing</t>
+          <t>quote plain scalars containing ": "; build with --verify before committing (the builder's yaml.safe_load is the parse check); CI's workbook step catches an unparsable spec; the regen generator parses its own output before writing</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>40e9544 (2026-10-16); new_regen_workflow.py parses before it writes</t>
+          <t>40e9544 (the quoted scalar, 2026-10-16); CI red at 0a54e5f, green from fdb5e39</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>a regen workflow on pull_request would fail at checkout for a fork PR</t>
+          <t>a regen workflow on pull_request would have failed at checkout for a fork PR (found in the pre-push review of a draft)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>no ref: on the checkout — the event's default ref (merge ref on pull_request)</t>
+          <t>no ref: on the checkout — the event's default ref (merge ref on pull_request); 41a9634 never emitted ref:</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>41a9634; references/github-actions-facts.md; test_inline_workflow_shape</t>
+          <t>references/github-actions-facts.md; test_inline_workflow_shape asserts no ref:</t>
         </is>
       </c>
     </row>

--- a/docs/EXECUTION_SURFACES_TOOLING.xlsx
+++ b/docs/EXECUTION_SURFACES_TOOLING.xlsx
@@ -534,7 +534,7 @@
 runs one generator and commits what changed as github-actions[bot] with a "Regenerated-by:" trailer that the ledger skips. The README
 index is the one layer that is Parallel across all three (same script, same arguments, same output); everything else is Conditional
 on "same commit" or Divergent because only the developer surface creates and only the bot surface commits unattended. Remediation
-rows U01–U09 record what this project corrected on the way: the hand path when no key exists, a tree check that failed only in CI,
+rows U01–U10 record what this project corrected on the way: the hand path when no key exists, a tree check that failed only in CI,
 a ledger check that needed full history, a workbook that is never byte-reproducible, a YAML pushed unparsed, and four review findings
 on the GitHub Actions skill fixed before the push.
 </t>
@@ -795,7 +795,7 @@
         <is>
           <t xml:space="preserve">Legend: Parity column colours — green Parallel, yellow Conditional, orange Divergent. Layers U0–U11 are the stages of the universal
 loop (install → recipe → apply → verify → commit → ledger → tree → workbook → index → generate workflows → review → push); Pipeline
-steps are the same loop as the operator runs it, in order, with the one LIVE gate (the push); Remediation rows U01–U09 are what
+steps are the same loop as the operator runs it, in order, with the one LIVE gate (the push); Remediation rows U01–U10 are what
 CloudBQ corrected between 2026-10-05 and 2026-10-16, each with the commit or test that holds the fix. Source: the repository on
 branch claude/cloud-run-bigquery-pipeline-e94ziy at d18a95f; the same files live in IC-DBT-BQ at 250dc6d.
 </t>
@@ -1972,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2351,6 +2351,43 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>610d41e; test_generator_without_pyyaml_and_bad_inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>the bot's first run on main ("Update README index", run 38958479320) was cancelled after 1 s: "Canceling since a deadlock was detected for concurrency group 'regenerate-Update README index-refs/heads/main' between a top level workflow and 'regenerate'"</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>the thin caller and the reusable workflow both declared a top-level concurrency group with the same value; GitHub treats the called workflow's group as the job's and refuses the self-deadlock</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>regenerate.yml declares no concurrency group; the inline workflow and the thin caller own it (new_regen_workflow.py; test_reusable_workflow_shape asserts the absence)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>this commit; the first bot run after it merges to main is the proof — no local tool evaluates GitHub's concurrency rules</t>
         </is>
       </c>
     </row>
